--- a/sim/resources/sample/EmployeeLevel.xlsx
+++ b/sim/resources/sample/EmployeeLevel.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="EmployeeLevel" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="215">
   <si>
     <t>ID</t>
   </si>
@@ -62,340 +62,349 @@
     <t>UpgradeCost</t>
   </si>
   <si>
-    <t>SkillValue</t>
+    <t>AttributeValue</t>
   </si>
   <si>
     <t>1024008_1000</t>
   </si>
   <si>
+    <t>3_100</t>
+  </si>
+  <si>
+    <t>1024008_1100</t>
+  </si>
+  <si>
+    <t>3_200</t>
+  </si>
+  <si>
+    <t>1024008_1200</t>
+  </si>
+  <si>
+    <t>1_300</t>
+  </si>
+  <si>
+    <t>1024008_1300</t>
+  </si>
+  <si>
+    <t>1_400</t>
+  </si>
+  <si>
+    <t>1024008_1400</t>
+  </si>
+  <si>
+    <t>1_500</t>
+  </si>
+  <si>
+    <t>1024008_1500</t>
+  </si>
+  <si>
+    <t>1_600</t>
+  </si>
+  <si>
+    <t>1024008_1600</t>
+  </si>
+  <si>
+    <t>1_700</t>
+  </si>
+  <si>
+    <t>1024008_1700</t>
+  </si>
+  <si>
+    <t>1_800</t>
+  </si>
+  <si>
+    <t>1024008_1800</t>
+  </si>
+  <si>
+    <t>1_900</t>
+  </si>
+  <si>
+    <t>1024008_1900</t>
+  </si>
+  <si>
+    <t>1_2000</t>
+  </si>
+  <si>
+    <t>1024008_5000</t>
+  </si>
+  <si>
+    <t>3_2100</t>
+  </si>
+  <si>
+    <t>1024008_5100</t>
+  </si>
+  <si>
+    <t>1_2200</t>
+  </si>
+  <si>
+    <t>1024008_5200</t>
+  </si>
+  <si>
+    <t>1_2300</t>
+  </si>
+  <si>
+    <t>1024008_5300</t>
+  </si>
+  <si>
+    <t>1_2400</t>
+  </si>
+  <si>
+    <t>1024008_5400</t>
+  </si>
+  <si>
+    <t>1_2500</t>
+  </si>
+  <si>
+    <t>1024008_5500</t>
+  </si>
+  <si>
+    <t>1_2600</t>
+  </si>
+  <si>
+    <t>1024008_5600</t>
+  </si>
+  <si>
+    <t>1_2700</t>
+  </si>
+  <si>
+    <t>1024008_5700</t>
+  </si>
+  <si>
+    <t>1_2800</t>
+  </si>
+  <si>
+    <t>1024008_5800</t>
+  </si>
+  <si>
+    <t>1_2900</t>
+  </si>
+  <si>
+    <t>1024008_5900</t>
+  </si>
+  <si>
+    <t>1_3000</t>
+  </si>
+  <si>
+    <t>1024008_10000</t>
+  </si>
+  <si>
+    <t>1_5000</t>
+  </si>
+  <si>
+    <t>1024008_10100</t>
+  </si>
+  <si>
+    <t>1_5100</t>
+  </si>
+  <si>
+    <t>1024008_10200</t>
+  </si>
+  <si>
+    <t>1_5200</t>
+  </si>
+  <si>
+    <t>1024008_10300</t>
+  </si>
+  <si>
+    <t>1_5300</t>
+  </si>
+  <si>
+    <t>1024008_10400</t>
+  </si>
+  <si>
+    <t>1_5400</t>
+  </si>
+  <si>
+    <t>1024008_10500</t>
+  </si>
+  <si>
+    <t>1_5500</t>
+  </si>
+  <si>
+    <t>1024008_10600</t>
+  </si>
+  <si>
+    <t>1_5600</t>
+  </si>
+  <si>
+    <t>1024008_10700</t>
+  </si>
+  <si>
+    <t>1_5700</t>
+  </si>
+  <si>
+    <t>1024008_10800</t>
+  </si>
+  <si>
+    <t>1_5800</t>
+  </si>
+  <si>
+    <t>1024008_10900</t>
+  </si>
+  <si>
+    <t>1_5900</t>
+  </si>
+  <si>
+    <t>1024008_15000</t>
+  </si>
+  <si>
+    <t>1_8000</t>
+  </si>
+  <si>
+    <t>1024008_15100</t>
+  </si>
+  <si>
+    <t>1_8100</t>
+  </si>
+  <si>
+    <t>1024008_15200</t>
+  </si>
+  <si>
+    <t>1_8200</t>
+  </si>
+  <si>
+    <t>1024008_15300</t>
+  </si>
+  <si>
+    <t>1_8300</t>
+  </si>
+  <si>
+    <t>1024008_15400</t>
+  </si>
+  <si>
+    <t>1_8400</t>
+  </si>
+  <si>
+    <t>1024008_15500</t>
+  </si>
+  <si>
+    <t>1_8500</t>
+  </si>
+  <si>
+    <t>1024008_15600</t>
+  </si>
+  <si>
+    <t>1_8600</t>
+  </si>
+  <si>
+    <t>1024008_15700</t>
+  </si>
+  <si>
+    <t>1_8700</t>
+  </si>
+  <si>
+    <t>1024008_15800</t>
+  </si>
+  <si>
+    <t>1_8800</t>
+  </si>
+  <si>
+    <t>1024008_15900</t>
+  </si>
+  <si>
+    <t>1_8900</t>
+  </si>
+  <si>
+    <t>1024008_20000</t>
+  </si>
+  <si>
+    <t>1_10000</t>
+  </si>
+  <si>
+    <t>1024008_20100</t>
+  </si>
+  <si>
+    <t>1_10100</t>
+  </si>
+  <si>
+    <t>1024008_20200</t>
+  </si>
+  <si>
+    <t>1_10200</t>
+  </si>
+  <si>
+    <t>1024008_20300</t>
+  </si>
+  <si>
+    <t>1_10300</t>
+  </si>
+  <si>
+    <t>1024008_20400</t>
+  </si>
+  <si>
+    <t>1_10400</t>
+  </si>
+  <si>
+    <t>1024008_20500</t>
+  </si>
+  <si>
+    <t>1_10500</t>
+  </si>
+  <si>
+    <t>1024008_20600</t>
+  </si>
+  <si>
+    <t>1_10600</t>
+  </si>
+  <si>
+    <t>1024008_20700</t>
+  </si>
+  <si>
+    <t>1_10700</t>
+  </si>
+  <si>
+    <t>1024008_20800</t>
+  </si>
+  <si>
+    <t>1_10800</t>
+  </si>
+  <si>
+    <t>1024008_20900</t>
+  </si>
+  <si>
+    <t>1_10900</t>
+  </si>
+  <si>
+    <t>1024009_1000</t>
+  </si>
+  <si>
     <t>1_100</t>
   </si>
   <si>
-    <t>1024008_1100</t>
+    <t>1024009_1100</t>
   </si>
   <si>
     <t>1_200</t>
   </si>
   <si>
-    <t>1024008_1200</t>
-  </si>
-  <si>
-    <t>1_300</t>
-  </si>
-  <si>
-    <t>1024008_1300</t>
-  </si>
-  <si>
-    <t>1_400</t>
-  </si>
-  <si>
-    <t>1024008_1400</t>
-  </si>
-  <si>
-    <t>1_500</t>
-  </si>
-  <si>
-    <t>1024008_1500</t>
-  </si>
-  <si>
-    <t>1_600</t>
-  </si>
-  <si>
-    <t>1024008_1600</t>
-  </si>
-  <si>
-    <t>1_700</t>
-  </si>
-  <si>
-    <t>1024008_1700</t>
-  </si>
-  <si>
-    <t>1_800</t>
-  </si>
-  <si>
-    <t>1024008_1800</t>
-  </si>
-  <si>
-    <t>1_900</t>
-  </si>
-  <si>
-    <t>1024008_1900</t>
-  </si>
-  <si>
-    <t>1_2000</t>
-  </si>
-  <si>
-    <t>1024008_5000</t>
+    <t>1024009_1200</t>
+  </si>
+  <si>
+    <t>1024009_1300</t>
+  </si>
+  <si>
+    <t>1024009_1400</t>
+  </si>
+  <si>
+    <t>1024009_1500</t>
+  </si>
+  <si>
+    <t>1024009_1600</t>
+  </si>
+  <si>
+    <t>1024009_1700</t>
+  </si>
+  <si>
+    <t>1024009_1800</t>
+  </si>
+  <si>
+    <t>1024009_1900</t>
+  </si>
+  <si>
+    <t>1024009_5000</t>
   </si>
   <si>
     <t>1_2100</t>
-  </si>
-  <si>
-    <t>1024008_5100</t>
-  </si>
-  <si>
-    <t>1_2200</t>
-  </si>
-  <si>
-    <t>1024008_5200</t>
-  </si>
-  <si>
-    <t>1_2300</t>
-  </si>
-  <si>
-    <t>1024008_5300</t>
-  </si>
-  <si>
-    <t>1_2400</t>
-  </si>
-  <si>
-    <t>1024008_5400</t>
-  </si>
-  <si>
-    <t>1_2500</t>
-  </si>
-  <si>
-    <t>1024008_5500</t>
-  </si>
-  <si>
-    <t>1_2600</t>
-  </si>
-  <si>
-    <t>1024008_5600</t>
-  </si>
-  <si>
-    <t>1_2700</t>
-  </si>
-  <si>
-    <t>1024008_5700</t>
-  </si>
-  <si>
-    <t>1_2800</t>
-  </si>
-  <si>
-    <t>1024008_5800</t>
-  </si>
-  <si>
-    <t>1_2900</t>
-  </si>
-  <si>
-    <t>1024008_5900</t>
-  </si>
-  <si>
-    <t>1_3000</t>
-  </si>
-  <si>
-    <t>1024008_10000</t>
-  </si>
-  <si>
-    <t>1_5000</t>
-  </si>
-  <si>
-    <t>1024008_10100</t>
-  </si>
-  <si>
-    <t>1_5100</t>
-  </si>
-  <si>
-    <t>1024008_10200</t>
-  </si>
-  <si>
-    <t>1_5200</t>
-  </si>
-  <si>
-    <t>1024008_10300</t>
-  </si>
-  <si>
-    <t>1_5300</t>
-  </si>
-  <si>
-    <t>1024008_10400</t>
-  </si>
-  <si>
-    <t>1_5400</t>
-  </si>
-  <si>
-    <t>1024008_10500</t>
-  </si>
-  <si>
-    <t>1_5500</t>
-  </si>
-  <si>
-    <t>1024008_10600</t>
-  </si>
-  <si>
-    <t>1_5600</t>
-  </si>
-  <si>
-    <t>1024008_10700</t>
-  </si>
-  <si>
-    <t>1_5700</t>
-  </si>
-  <si>
-    <t>1024008_10800</t>
-  </si>
-  <si>
-    <t>1_5800</t>
-  </si>
-  <si>
-    <t>1024008_10900</t>
-  </si>
-  <si>
-    <t>1_5900</t>
-  </si>
-  <si>
-    <t>1024008_15000</t>
-  </si>
-  <si>
-    <t>1_8000</t>
-  </si>
-  <si>
-    <t>1024008_15100</t>
-  </si>
-  <si>
-    <t>1_8100</t>
-  </si>
-  <si>
-    <t>1024008_15200</t>
-  </si>
-  <si>
-    <t>1_8200</t>
-  </si>
-  <si>
-    <t>1024008_15300</t>
-  </si>
-  <si>
-    <t>1_8300</t>
-  </si>
-  <si>
-    <t>1024008_15400</t>
-  </si>
-  <si>
-    <t>1_8400</t>
-  </si>
-  <si>
-    <t>1024008_15500</t>
-  </si>
-  <si>
-    <t>1_8500</t>
-  </si>
-  <si>
-    <t>1024008_15600</t>
-  </si>
-  <si>
-    <t>1_8600</t>
-  </si>
-  <si>
-    <t>1024008_15700</t>
-  </si>
-  <si>
-    <t>1_8700</t>
-  </si>
-  <si>
-    <t>1024008_15800</t>
-  </si>
-  <si>
-    <t>1_8800</t>
-  </si>
-  <si>
-    <t>1024008_15900</t>
-  </si>
-  <si>
-    <t>1_8900</t>
-  </si>
-  <si>
-    <t>1024008_20000</t>
-  </si>
-  <si>
-    <t>1_10000</t>
-  </si>
-  <si>
-    <t>1024008_20100</t>
-  </si>
-  <si>
-    <t>1_10100</t>
-  </si>
-  <si>
-    <t>1024008_20200</t>
-  </si>
-  <si>
-    <t>1_10200</t>
-  </si>
-  <si>
-    <t>1024008_20300</t>
-  </si>
-  <si>
-    <t>1_10300</t>
-  </si>
-  <si>
-    <t>1024008_20400</t>
-  </si>
-  <si>
-    <t>1_10400</t>
-  </si>
-  <si>
-    <t>1024008_20500</t>
-  </si>
-  <si>
-    <t>1_10500</t>
-  </si>
-  <si>
-    <t>1024008_20600</t>
-  </si>
-  <si>
-    <t>1_10600</t>
-  </si>
-  <si>
-    <t>1024008_20700</t>
-  </si>
-  <si>
-    <t>1_10700</t>
-  </si>
-  <si>
-    <t>1024008_20800</t>
-  </si>
-  <si>
-    <t>1_10800</t>
-  </si>
-  <si>
-    <t>1024008_20900</t>
-  </si>
-  <si>
-    <t>1_10900</t>
-  </si>
-  <si>
-    <t>1024009_1000</t>
-  </si>
-  <si>
-    <t>1024009_1100</t>
-  </si>
-  <si>
-    <t>1024009_1200</t>
-  </si>
-  <si>
-    <t>1024009_1300</t>
-  </si>
-  <si>
-    <t>1024009_1400</t>
-  </si>
-  <si>
-    <t>1024009_1500</t>
-  </si>
-  <si>
-    <t>1024009_1600</t>
-  </si>
-  <si>
-    <t>1024009_1700</t>
-  </si>
-  <si>
-    <t>1024009_1800</t>
-  </si>
-  <si>
-    <t>1024009_1900</t>
-  </si>
-  <si>
-    <t>1024009_5000</t>
   </si>
   <si>
     <t>1024009_5100</t>
@@ -2826,7 +2835,7 @@
         <v>112</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>13</v>
+        <v>113</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -2841,10 +2850,10 @@
         <v>2</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>15</v>
+        <v>115</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -2859,7 +2868,7 @@
         <v>3</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E57" s="1" t="s">
         <v>17</v>
@@ -2877,7 +2886,7 @@
         <v>4</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E58" s="1" t="s">
         <v>19</v>
@@ -2895,7 +2904,7 @@
         <v>5</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>21</v>
@@ -2913,7 +2922,7 @@
         <v>6</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E60" s="1" t="s">
         <v>23</v>
@@ -2931,7 +2940,7 @@
         <v>7</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>25</v>
@@ -2949,7 +2958,7 @@
         <v>8</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E62" s="1" t="s">
         <v>27</v>
@@ -2967,7 +2976,7 @@
         <v>9</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E63" s="1" t="s">
         <v>29</v>
@@ -2985,7 +2994,7 @@
         <v>10</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E64" s="1" t="s">
         <v>31</v>
@@ -3003,10 +3012,10 @@
         <v>1</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>33</v>
+        <v>125</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -3021,7 +3030,7 @@
         <v>2</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E66" s="1" t="s">
         <v>35</v>
@@ -3039,7 +3048,7 @@
         <v>3</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E67" s="1" t="s">
         <v>37</v>
@@ -3057,7 +3066,7 @@
         <v>4</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E68" s="1" t="s">
         <v>39</v>
@@ -3075,7 +3084,7 @@
         <v>5</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E69" s="1" t="s">
         <v>41</v>
@@ -3093,7 +3102,7 @@
         <v>6</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="E70" s="1" t="s">
         <v>43</v>
@@ -3111,7 +3120,7 @@
         <v>7</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E71" s="1" t="s">
         <v>45</v>
@@ -3129,7 +3138,7 @@
         <v>8</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="E72" s="1" t="s">
         <v>47</v>
@@ -3147,7 +3156,7 @@
         <v>9</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="E73" s="1" t="s">
         <v>49</v>
@@ -3165,7 +3174,7 @@
         <v>10</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="E74" s="1" t="s">
         <v>51</v>
@@ -3183,7 +3192,7 @@
         <v>1</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="E75" s="1" t="s">
         <v>53</v>
@@ -3201,7 +3210,7 @@
         <v>2</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="E76" s="1" t="s">
         <v>55</v>
@@ -3219,7 +3228,7 @@
         <v>3</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E77" s="1" t="s">
         <v>57</v>
@@ -3237,7 +3246,7 @@
         <v>4</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="E78" s="1" t="s">
         <v>59</v>
@@ -3255,7 +3264,7 @@
         <v>5</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E79" s="1" t="s">
         <v>61</v>
@@ -3273,7 +3282,7 @@
         <v>6</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E80" s="1" t="s">
         <v>63</v>
@@ -3291,7 +3300,7 @@
         <v>7</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="E81" s="1" t="s">
         <v>65</v>
@@ -3309,7 +3318,7 @@
         <v>8</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="E82" s="1" t="s">
         <v>67</v>
@@ -3327,7 +3336,7 @@
         <v>9</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E83" s="1" t="s">
         <v>69</v>
@@ -3345,7 +3354,7 @@
         <v>10</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E84" s="1" t="s">
         <v>71</v>
@@ -3363,7 +3372,7 @@
         <v>1</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E85" s="1" t="s">
         <v>73</v>
@@ -3381,7 +3390,7 @@
         <v>2</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E86" s="1" t="s">
         <v>75</v>
@@ -3399,7 +3408,7 @@
         <v>3</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E87" s="1" t="s">
         <v>77</v>
@@ -3417,7 +3426,7 @@
         <v>4</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E88" s="1" t="s">
         <v>79</v>
@@ -3435,7 +3444,7 @@
         <v>5</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="E89" s="1" t="s">
         <v>81</v>
@@ -3453,7 +3462,7 @@
         <v>6</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="E90" s="1" t="s">
         <v>83</v>
@@ -3471,7 +3480,7 @@
         <v>7</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="E91" s="1" t="s">
         <v>85</v>
@@ -3489,7 +3498,7 @@
         <v>8</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="E92" s="1" t="s">
         <v>87</v>
@@ -3507,7 +3516,7 @@
         <v>9</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="E93" s="1" t="s">
         <v>89</v>
@@ -3525,7 +3534,7 @@
         <v>10</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="E94" s="1" t="s">
         <v>91</v>
@@ -3543,7 +3552,7 @@
         <v>1</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="E95" s="1" t="s">
         <v>93</v>
@@ -3561,7 +3570,7 @@
         <v>2</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="E96" s="1" t="s">
         <v>95</v>
@@ -3579,7 +3588,7 @@
         <v>3</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="E97" s="1" t="s">
         <v>97</v>
@@ -3597,7 +3606,7 @@
         <v>4</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="E98" s="1" t="s">
         <v>99</v>
@@ -3615,7 +3624,7 @@
         <v>5</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E99" s="1" t="s">
         <v>101</v>
@@ -3633,7 +3642,7 @@
         <v>6</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E100" s="1" t="s">
         <v>103</v>
@@ -3651,7 +3660,7 @@
         <v>7</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="E101" s="1" t="s">
         <v>105</v>
@@ -3669,7 +3678,7 @@
         <v>8</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="E102" s="1" t="s">
         <v>107</v>
@@ -3687,7 +3696,7 @@
         <v>9</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="E103" s="1" t="s">
         <v>109</v>
@@ -3705,7 +3714,7 @@
         <v>10</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="E104" s="1" t="s">
         <v>111</v>
@@ -3723,10 +3732,10 @@
         <v>1</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>13</v>
+        <v>113</v>
       </c>
     </row>
     <row r="106" spans="1:5">
@@ -3741,10 +3750,10 @@
         <v>2</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>15</v>
+        <v>115</v>
       </c>
     </row>
     <row r="107" spans="1:5">
@@ -3759,7 +3768,7 @@
         <v>3</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="E107" s="1" t="s">
         <v>17</v>
@@ -3777,7 +3786,7 @@
         <v>4</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="E108" s="1" t="s">
         <v>19</v>
@@ -3795,7 +3804,7 @@
         <v>5</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="E109" s="1" t="s">
         <v>21</v>
@@ -3813,7 +3822,7 @@
         <v>6</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="E110" s="1" t="s">
         <v>23</v>
@@ -3831,7 +3840,7 @@
         <v>7</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="E111" s="1" t="s">
         <v>25</v>
@@ -3849,7 +3858,7 @@
         <v>8</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="E112" s="1" t="s">
         <v>27</v>
@@ -3867,7 +3876,7 @@
         <v>9</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="E113" s="1" t="s">
         <v>29</v>
@@ -3885,7 +3894,7 @@
         <v>10</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="E114" s="1" t="s">
         <v>31</v>
@@ -3903,10 +3912,10 @@
         <v>1</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>33</v>
+        <v>125</v>
       </c>
     </row>
     <row r="116" spans="1:5">
@@ -3921,7 +3930,7 @@
         <v>2</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="E116" s="1" t="s">
         <v>35</v>
@@ -3939,7 +3948,7 @@
         <v>3</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="E117" s="1" t="s">
         <v>37</v>
@@ -3957,7 +3966,7 @@
         <v>4</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E118" s="1" t="s">
         <v>39</v>
@@ -3975,7 +3984,7 @@
         <v>5</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="E119" s="1" t="s">
         <v>41</v>
@@ -3993,7 +4002,7 @@
         <v>6</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E120" s="1" t="s">
         <v>43</v>
@@ -4011,7 +4020,7 @@
         <v>7</v>
       </c>
       <c r="D121" s="3" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E121" s="1" t="s">
         <v>45</v>
@@ -4029,7 +4038,7 @@
         <v>8</v>
       </c>
       <c r="D122" s="3" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="E122" s="1" t="s">
         <v>47</v>
@@ -4047,7 +4056,7 @@
         <v>9</v>
       </c>
       <c r="D123" s="3" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="E123" s="1" t="s">
         <v>49</v>
@@ -4065,7 +4074,7 @@
         <v>10</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="E124" s="1" t="s">
         <v>51</v>
@@ -4083,7 +4092,7 @@
         <v>1</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="E125" s="1" t="s">
         <v>53</v>
@@ -4101,7 +4110,7 @@
         <v>2</v>
       </c>
       <c r="D126" s="3" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="E126" s="1" t="s">
         <v>55</v>
@@ -4119,7 +4128,7 @@
         <v>3</v>
       </c>
       <c r="D127" s="3" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E127" s="1" t="s">
         <v>57</v>
@@ -4137,7 +4146,7 @@
         <v>4</v>
       </c>
       <c r="D128" s="3" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="E128" s="1" t="s">
         <v>59</v>
@@ -4155,7 +4164,7 @@
         <v>5</v>
       </c>
       <c r="D129" s="3" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="E129" s="1" t="s">
         <v>61</v>
@@ -4173,7 +4182,7 @@
         <v>6</v>
       </c>
       <c r="D130" s="3" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="E130" s="1" t="s">
         <v>63</v>
@@ -4191,7 +4200,7 @@
         <v>7</v>
       </c>
       <c r="D131" s="3" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="E131" s="1" t="s">
         <v>65</v>
@@ -4209,7 +4218,7 @@
         <v>8</v>
       </c>
       <c r="D132" s="3" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="E132" s="1" t="s">
         <v>67</v>
@@ -4227,7 +4236,7 @@
         <v>9</v>
       </c>
       <c r="D133" s="3" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E133" s="1" t="s">
         <v>69</v>
@@ -4245,7 +4254,7 @@
         <v>10</v>
       </c>
       <c r="D134" s="3" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="E134" s="1" t="s">
         <v>71</v>
@@ -4263,7 +4272,7 @@
         <v>1</v>
       </c>
       <c r="D135" s="3" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="E135" s="1" t="s">
         <v>73</v>
@@ -4281,7 +4290,7 @@
         <v>2</v>
       </c>
       <c r="D136" s="3" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="E136" s="1" t="s">
         <v>75</v>
@@ -4299,7 +4308,7 @@
         <v>3</v>
       </c>
       <c r="D137" s="3" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="E137" s="1" t="s">
         <v>77</v>
@@ -4317,7 +4326,7 @@
         <v>4</v>
       </c>
       <c r="D138" s="3" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="E138" s="1" t="s">
         <v>79</v>
@@ -4335,7 +4344,7 @@
         <v>5</v>
       </c>
       <c r="D139" s="3" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="E139" s="1" t="s">
         <v>81</v>
@@ -4353,7 +4362,7 @@
         <v>6</v>
       </c>
       <c r="D140" s="3" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="E140" s="1" t="s">
         <v>83</v>
@@ -4371,7 +4380,7 @@
         <v>7</v>
       </c>
       <c r="D141" s="3" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="E141" s="1" t="s">
         <v>85</v>
@@ -4389,7 +4398,7 @@
         <v>8</v>
       </c>
       <c r="D142" s="3" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="E142" s="1" t="s">
         <v>87</v>
@@ -4407,7 +4416,7 @@
         <v>9</v>
       </c>
       <c r="D143" s="3" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="E143" s="1" t="s">
         <v>89</v>
@@ -4425,7 +4434,7 @@
         <v>10</v>
       </c>
       <c r="D144" s="3" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="E144" s="1" t="s">
         <v>91</v>
@@ -4443,7 +4452,7 @@
         <v>1</v>
       </c>
       <c r="D145" s="3" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="E145" s="1" t="s">
         <v>93</v>
@@ -4461,7 +4470,7 @@
         <v>2</v>
       </c>
       <c r="D146" s="3" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="E146" s="1" t="s">
         <v>95</v>
@@ -4479,7 +4488,7 @@
         <v>3</v>
       </c>
       <c r="D147" s="3" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="E147" s="1" t="s">
         <v>97</v>
@@ -4497,7 +4506,7 @@
         <v>4</v>
       </c>
       <c r="D148" s="3" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="E148" s="1" t="s">
         <v>99</v>
@@ -4515,7 +4524,7 @@
         <v>5</v>
       </c>
       <c r="D149" s="3" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="E149" s="1" t="s">
         <v>101</v>
@@ -4533,7 +4542,7 @@
         <v>6</v>
       </c>
       <c r="D150" s="3" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="E150" s="1" t="s">
         <v>103</v>
@@ -4551,7 +4560,7 @@
         <v>7</v>
       </c>
       <c r="D151" s="3" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="E151" s="1" t="s">
         <v>105</v>
@@ -4569,7 +4578,7 @@
         <v>8</v>
       </c>
       <c r="D152" s="3" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="E152" s="1" t="s">
         <v>107</v>
@@ -4587,7 +4596,7 @@
         <v>9</v>
       </c>
       <c r="D153" s="3" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="E153" s="1" t="s">
         <v>109</v>
@@ -4605,7 +4614,7 @@
         <v>10</v>
       </c>
       <c r="D154" s="3" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="E154" s="1" t="s">
         <v>111</v>
